--- a/CONTROLE PAGAMENTOS.xlsx
+++ b/CONTROLE PAGAMENTOS.xlsx
@@ -1954,7 +1954,7 @@
         <v>10000</v>
       </c>
       <c r="F2" s="9">
-        <v>45894</v>
+        <v>46303</v>
       </c>
       <c r="G2" s="9">
         <v>45894</v>
@@ -1976,15 +1976,15 @@
       </c>
       <c r="L2" t="str" s="12">
         <f>IF(OR(ISBLANK(PARCELAS[[#This Row],[DATA PAGAMENTO]]),DAY(PARCELAS[[#This Row],[DATA PAGAMENTO]])=0),"",TEXT(DAY(PARCELAS[[#This Row],[DATA PAGAMENTO]]),"00"))</f>
-        <v>25</v>
+        <v>08</v>
       </c>
       <c r="M2" t="str" s="13">
         <f>IF(ISBLANK(PARCELAS[[#This Row],[DATA PAGAMENTO]]),"",INDEX(MESES[MÊS],MATCH(MONTH(PARCELAS[[#This Row],[DATA PAGAMENTO]]),MESES[N],0)))</f>
-        <v>agosto</v>
+        <v>outubro</v>
       </c>
       <c r="N2" s="12">
         <f>IF(OR(ISBLANK(PARCELAS[[#This Row],[DATA PAGAMENTO]]),YEAR(PARCELAS[[#This Row],[DATA PAGAMENTO]])=1900),"",YEAR(PARCELAS[[#This Row],[DATA PAGAMENTO]]))</f>
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="O2" t="s">
         <v>43</v>
